--- a/Files/KALYAN MORNING PENAL.xlsx
+++ b/Files/KALYAN MORNING PENAL.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$192</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$193</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -1583,6 +1583,9 @@
   </x:si>
   <x:si>
     <x:t>22/06/2026 to 30/06/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31/08/2026 to 06/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -2041,7 +2044,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V192"/>
+  <x:dimension ref="A1:V193"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -15059,53 +15062,121 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="H192" s="3" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="I192" s="3" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J192" s="3" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="K192" s="3" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="L192" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="M192" s="3" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="N192" s="3" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="O192" s="3" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="P192" s="3" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="Q192" s="3" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="R192" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S192" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="T192" s="3" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="U192" s="3" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="V192" s="3" t="s">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:22">
+      <x:c r="A193" s="3" t="s">
         <x:v>522</x:v>
       </x:c>
-      <x:c r="I192" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="J192" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="K192" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="L192" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="M192" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="N192" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="O192" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="P192" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="Q192" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="R192" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="S192" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="T192" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="U192" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="V192" s="3" t="s">
-        <x:v>522</x:v>
+      <x:c r="B193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="C193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="D193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="E193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="F193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="G193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="H193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="I193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="J193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="K193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="L193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="M193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="N193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="O193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="P193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="Q193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="R193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="S193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="T193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="U193" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="V193" s="3" t="s">
+        <x:v>523</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V192"/>
+  <x:autoFilter ref="A1:V193"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -15128,39 +15199,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>523</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>524</x:v>
+        <x:v>525</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>525</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>526</x:v>
+        <x:v>527</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>527</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>528</x:v>
+        <x:v>529</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>529</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>530</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -15168,10 +15239,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>521</x:v>
+        <x:v>522</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Files/KALYAN MORNING PENAL.xlsx
+++ b/Files/KALYAN MORNING PENAL.xlsx
@@ -15112,13 +15112,13 @@
         <x:v>522</x:v>
       </x:c>
       <x:c r="B193" s="3" t="s">
-        <x:v>523</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C193" s="3" t="s">
-        <x:v>523</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D193" s="3" t="s">
-        <x:v>523</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E193" s="3" t="s">
         <x:v>523</x:v>
